--- a/downloads/forms/power-of-attorney.xlsx
+++ b/downloads/forms/power-of-attorney.xlsx
@@ -653,7 +653,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="6" t="n"/>
     </row>
-    <row r="8" ht="130.3937007874016" customHeight="1">
+    <row r="8" ht="198.4251968503937" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
